--- a/ibiden/dist/20261028_Ibiden個股模型_v0.3.xlsx
+++ b/ibiden/dist/20261028_Ibiden個股模型_v0.3.xlsx
@@ -15366,16 +15366,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">stockanalysis</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（口徑：未來 </t>
+      <t xml:space="preserve">stockanalysis 2026-10-16 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">取值（股價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9,764</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；口徑：未來 </t>
     </r>
     <r>
       <rPr>
@@ -15394,7 +15413,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">個月共識，頁面未明示）</t>
+      <t xml:space="preserve">個月共識，頁面未明示；隨股價每日變動）</t>
     </r>
   </si>
   <si>
